--- a/src/beastmistress/assets/data/combatants.xlsx
+++ b/src/beastmistress/assets/data/combatants.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="19">
   <si>
     <t>UniqueID</t>
   </si>
@@ -49,9 +49,6 @@
     <t>Magda Blaine</t>
   </si>
   <si>
-    <t>Thorn</t>
-  </si>
-  <si>
     <t>NONE</t>
   </si>
   <si>
@@ -65,6 +62,15 @@
   </si>
   <si>
     <t>Shelly</t>
+  </si>
+  <si>
+    <t>DebugBeast</t>
+  </si>
+  <si>
+    <t>Splash</t>
+  </si>
+  <si>
+    <t>Thorn,Splash,Sunshine,Natural Healing</t>
   </si>
 </sst>
 </file>
@@ -440,7 +446,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>3</v>
@@ -469,28 +475,28 @@
         <v>10</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="J2" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
